--- a/data/trans_orig/MCS12_SP-Clase-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud mental (SF12)</t>
+          <t>Puntuación media del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,36; 53,61</t>
+          <t>52,31; 53,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,82; 53,2</t>
+          <t>51,85; 53,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,1; 53,5</t>
+          <t>52,23; 53,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,76; 53,26</t>
+          <t>51,77; 53,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,55; 52,37</t>
+          <t>50,51; 52,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,73; 52,57</t>
+          <t>50,77; 52,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,54; 53,26</t>
+          <t>51,43; 53,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,53; 52,79</t>
+          <t>51,55; 52,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,9; 52,92</t>
+          <t>51,88; 52,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,61; 52,76</t>
+          <t>51,65; 52,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,13; 53,19</t>
+          <t>52,16; 53,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,84; 52,84</t>
+          <t>51,81; 52,87</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,44; 53,87</t>
+          <t>52,42; 53,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,56; 53,15</t>
+          <t>51,56; 53,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,78; 53,4</t>
+          <t>51,81; 53,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,87; 54,35</t>
+          <t>52,88; 54,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,8; 51,52</t>
+          <t>49,73; 51,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,56; 50,7</t>
+          <t>48,58; 50,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,98; 52,55</t>
+          <t>50,99; 52,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,46; 52,04</t>
+          <t>50,38; 52,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,35; 52,54</t>
+          <t>51,31; 52,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,73; 52,79</t>
+          <t>51,65; 52,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,97; 53,08</t>
+          <t>51,99; 53,1</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,93; 53,07</t>
+          <t>51,9; 53,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,7; 52,1</t>
+          <t>50,75; 52,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,12; 52,59</t>
+          <t>51,2; 52,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,75; 54,44</t>
+          <t>51,58; 54,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,75; 51,8</t>
+          <t>48,74; 51,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,24; 49,84</t>
+          <t>47,18; 49,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,29; 50,73</t>
+          <t>47,35; 50,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,17; 51,45</t>
+          <t>49,2; 51,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,36; 52,52</t>
+          <t>51,44; 52,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,92; 51,15</t>
+          <t>50,01; 51,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,59; 51,91</t>
+          <t>50,55; 51,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,29; 54,04</t>
+          <t>51,29; 53,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,39; 52,25</t>
+          <t>51,42; 52,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,9; 51,94</t>
+          <t>50,95; 51,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,86; 52,74</t>
+          <t>51,82; 52,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,86; 52,88</t>
+          <t>51,84; 52,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,9; 51,18</t>
+          <t>49,88; 51,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,68; 50,21</t>
+          <t>48,74; 50,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,7; 51,15</t>
+          <t>49,76; 51,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,12; 51,42</t>
+          <t>47,19; 51,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,98; 51,69</t>
+          <t>50,96; 51,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,21; 51,14</t>
+          <t>50,3; 51,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,14; 51,91</t>
+          <t>51,15; 51,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,05; 52,04</t>
+          <t>48,99; 52,08</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,66; 53,27</t>
+          <t>51,55; 53,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,64; 52,99</t>
+          <t>51,62; 52,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,06; 52,4</t>
+          <t>51,05; 52,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,19; 52,81</t>
+          <t>51,15; 52,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,47; 51,0</t>
+          <t>49,59; 51,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,97; 48,63</t>
+          <t>46,95; 48,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,13; 49,63</t>
+          <t>48,06; 49,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,42; 51,45</t>
+          <t>49,28; 51,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,56; 51,7</t>
+          <t>50,59; 51,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,04; 50,15</t>
+          <t>49,06; 50,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,64; 50,71</t>
+          <t>49,62; 50,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,2; 51,48</t>
+          <t>50,26; 51,48</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,36; 54,82</t>
+          <t>53,29; 54,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,29; 54,87</t>
+          <t>53,23; 54,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,46; 55,09</t>
+          <t>53,36; 55,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,96; 55,67</t>
+          <t>52,92; 55,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,48; 51,44</t>
+          <t>50,45; 51,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,66; 49,93</t>
+          <t>48,62; 49,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,34; 51,58</t>
+          <t>50,44; 51,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,58; 50,99</t>
+          <t>49,66; 51,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,13; 52,02</t>
+          <t>51,18; 52,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49,67; 50,71</t>
+          <t>49,7; 50,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,2; 52,22</t>
+          <t>51,23; 52,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50,68; 51,91</t>
+          <t>50,73; 51,95</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,29; 52,78</t>
+          <t>52,3; 52,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,16; 52,7</t>
+          <t>52,17; 52,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,49; 53,32</t>
+          <t>52,46; 53,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,08</t>
+          <t>50,45; 51,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,85; 49,56</t>
+          <t>48,83; 49,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,27; 50,9</t>
+          <t>50,27; 50,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,24; 51,01</t>
+          <t>49,09; 50,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,84</t>
+          <t>51,47; 51,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,39; 50,86</t>
+          <t>50,38; 50,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,71</t>
+          <t>51,26; 51,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,76; 51,99</t>
+          <t>50,85; 52,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP-Clase-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52,57</t>
+          <t>52,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,19</t>
+          <t>52,03</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,39</t>
+          <t>52,37</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,31; 53,59</t>
+          <t>52,29; 53,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,85; 53,25</t>
+          <t>51,85; 53,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,23; 53,55</t>
+          <t>52,21; 53,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,77; 53,24</t>
+          <t>51,78; 53,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,51; 52,37</t>
+          <t>50,61; 52,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,77; 52,64</t>
+          <t>50,69; 52,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 53,22</t>
+          <t>51,54; 53,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,55; 52,88</t>
+          <t>51,32; 52,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,88; 52,94</t>
+          <t>51,92; 52,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,65; 52,77</t>
+          <t>51,65; 52,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,16; 53,21</t>
+          <t>52,15; 53,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,81; 52,87</t>
+          <t>51,87; 52,79</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,68</t>
+          <t>53,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,29</t>
+          <t>51,23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,58</t>
+          <t>52,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,42; 53,87</t>
+          <t>52,43; 53,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,56; 53,07</t>
+          <t>51,51; 53,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,81; 53,39</t>
+          <t>51,88; 53,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,88; 54,33</t>
+          <t>52,84; 54,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,73; 51,47</t>
+          <t>49,84; 51,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,58; 50,69</t>
+          <t>48,64; 50,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,99; 52,57</t>
+          <t>51,02; 52,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,38; 52,02</t>
+          <t>50,3; 51,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,31; 52,48</t>
+          <t>51,36; 52,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,54; 51,83</t>
+          <t>50,48; 51,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,65; 52,77</t>
+          <t>51,65; 52,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,99; 53,1</t>
+          <t>51,97; 53,03</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53,07</t>
+          <t>52,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,57</t>
+          <t>50,66</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,57</t>
+          <t>51,62</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,9; 53,06</t>
+          <t>51,88; 53,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,75; 52,11</t>
+          <t>50,74; 52,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,2; 52,57</t>
+          <t>51,23; 52,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,58; 54,4</t>
+          <t>51,09; 52,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,74; 51,67</t>
+          <t>48,62; 51,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,18; 49,85</t>
+          <t>47,02; 49,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,35; 50,75</t>
+          <t>47,34; 51,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,2; 51,58</t>
+          <t>49,42; 51,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,44; 52,53</t>
+          <t>51,37; 52,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,01; 51,26</t>
+          <t>49,92; 51,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,55; 51,96</t>
+          <t>50,57; 52,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,29; 53,91</t>
+          <t>50,86; 52,27</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,38</t>
+          <t>52,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,82</t>
+          <t>51,17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,13</t>
+          <t>51,85</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,42; 52,23</t>
+          <t>51,38; 52,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,95; 51,99</t>
+          <t>50,95; 52,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,82; 52,75</t>
+          <t>51,8; 52,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,84; 52,93</t>
+          <t>51,8; 52,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,88; 51,22</t>
+          <t>49,86; 51,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,74; 50,26</t>
+          <t>48,78; 50,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,76; 51,08</t>
+          <t>49,82; 51,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,19; 51,4</t>
+          <t>50,56; 51,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,96; 51,7</t>
+          <t>50,97; 51,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,3; 51,12</t>
+          <t>50,26; 51,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,15; 51,89</t>
+          <t>51,18; 51,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,99; 52,08</t>
+          <t>51,48; 52,2</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52,01</t>
+          <t>52,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,15</t>
+          <t>49,55</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,82</t>
+          <t>50,63</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,55; 53,28</t>
+          <t>51,65; 53,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,62; 52,95</t>
+          <t>51,66; 52,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,05; 52,35</t>
+          <t>51,06; 52,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,8</t>
+          <t>51,38; 52,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,59; 51,09</t>
+          <t>49,54; 51,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,95; 48,55</t>
+          <t>46,97; 48,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,06; 49,59</t>
+          <t>48,09; 49,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,28; 51,19</t>
+          <t>48,9; 50,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,59; 51,71</t>
+          <t>50,53; 51,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,06; 50,19</t>
+          <t>49,07; 50,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,62; 50,72</t>
+          <t>49,69; 50,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,26; 51,48</t>
+          <t>50,13; 51,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54,59</t>
+          <t>54,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>50,32</t>
+          <t>50,43</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,36</t>
+          <t>51,26</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,29; 54,76</t>
+          <t>53,32; 54,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,23; 54,86</t>
+          <t>53,26; 54,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,36; 55,04</t>
+          <t>53,41; 55,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,92; 55,58</t>
+          <t>52,55; 55,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,47</t>
+          <t>50,5; 51,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,62; 49,84</t>
+          <t>48,58; 49,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,44; 51,66</t>
+          <t>50,4; 51,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,66; 51,03</t>
+          <t>49,76; 51,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,18; 52,0</t>
+          <t>51,17; 52,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49,7; 50,76</t>
+          <t>49,67; 50,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,23; 52,25</t>
+          <t>51,21; 52,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50,73; 51,95</t>
+          <t>50,58; 51,83</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52,83</t>
+          <t>52,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>50,49</t>
+          <t>50,73</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,63</t>
+          <t>51,66</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,3; 52,82</t>
+          <t>52,31; 52,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,78; 52,33</t>
+          <t>51,77; 52,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,17; 52,73</t>
+          <t>52,17; 52,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,46; 53,29</t>
+          <t>52,35; 52,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,05</t>
+          <t>50,46; 51,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,83; 49,55</t>
+          <t>48,84; 49,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,27; 50,93</t>
+          <t>50,23; 50,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,09; 50,99</t>
+          <t>50,43; 50,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,83</t>
+          <t>51,43; 51,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,38; 50,83</t>
+          <t>50,37; 50,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,26; 51,7</t>
+          <t>51,25; 51,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,85; 52,0</t>
+          <t>51,45; 51,87</t>
         </is>
       </c>
     </row>
